--- a/tame_output/ON/bt/strategyON_20240411.xlsx
+++ b/tame_output/ON/bt/strategyON_20240411.xlsx
@@ -45941,10 +45941,10 @@
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.562925594421194</v>
+        <v>-3.563076551463589</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.674299586796811</v>
+        <v>1.674239203979853</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.2037738619551732</v>

--- a/tame_output/ON/bt/strategyON_20240411.xlsx
+++ b/tame_output/ON/bt/strategyON_20240411.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>59.5%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.5%</t>
+          <t>-77.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.0%</t>
+          <t>117.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.2%</t>
+          <t>136.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-694.2%</t>
+          <t>-685.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-55.6%</t>
+          <t>-55.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.0%</t>
+          <t>-72.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.7%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>499.7%</t>
+          <t>501.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-517.9%</t>
+          <t>-509.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-272.3%</t>
+          <t>-268.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-43.4%</t>
+          <t>-43.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>129.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-208.8%</t>
+          <t>-205.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.3%</t>
+          <t>-26.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-36.0%</t>
+          <t>-35.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-21.7%</t>
+          <t>-19.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-153.7%</t>
+          <t>-158.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-244.4%</t>
+          <t>-235.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.4%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1471,27 +1471,27 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-31.1%</t>
+          <t>-30.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-148.3%</t>
+          <t>-143.1%</t>
         </is>
       </c>
     </row>
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.23917305058595</v>
+        <v>-10.153375272995</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.9671540563548651</v>
+        <v>-0.9328349453184841</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.39932568372122</v>
+        <v>-2.313527906130268</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.689276177960532</v>
+        <v>1.740754844515103</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.23269690379239</v>
+        <v>-10.14689912620144</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.9615218470156717</v>
+        <v>-0.9272027359792916</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.39284953692766</v>
+        <v>-2.307051759336709</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.696203616658437</v>
+        <v>1.747682283213008</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.22900597883598</v>
+        <v>-10.14320820124503</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.9600454770331077</v>
+        <v>-0.9257263659967276</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.39284953692766</v>
+        <v>-2.307051759336709</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.696203616658437</v>
+        <v>1.747682283213008</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.43326415416585</v>
+        <v>-10.34746637657489</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.036235550046411</v>
+        <v>-1.001916439010031</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.520488481541649</v>
+        <v>-2.434690703950698</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.625133447008686</v>
+        <v>1.676612113563257</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.59390318065421</v>
+        <v>-10.50810540306326</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.096008606157321</v>
+        <v>-1.061689495120941</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.635221954544045</v>
+        <v>-2.549424176953093</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.560775917691684</v>
+        <v>1.612254584246255</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.52043334898676</v>
+        <v>-10.43463557139581</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.05124897199692</v>
+        <v>-1.01692986096054</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.561752122876596</v>
+        <v>-2.475954345285645</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.620229518185575</v>
+        <v>1.671708184740145</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.69555776637331</v>
+        <v>-10.60975998878235</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.106743518204021</v>
+        <v>-1.07242440716764</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.73687654026314</v>
+        <v>-2.651078762672189</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.529710088501165</v>
+        <v>1.581188755055736</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.93000986038779</v>
+        <v>-10.84421208279684</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.207743520711413</v>
+        <v>-1.173424409675032</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.73687654026314</v>
+        <v>-2.651078762672189</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.522490923599569</v>
+        <v>1.57396959015414</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.21781370492503</v>
+        <v>-11.13201592733408</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.329537249300284</v>
+        <v>-1.295218138263904</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.024680384800378</v>
+        <v>-2.938882607209427</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.34313642610325</v>
+        <v>1.394615092657821</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.44763815208886</v>
+        <v>-11.36184037449791</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.420351238327258</v>
+        <v>-1.386032127290878</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.187327921870539</v>
+        <v>-3.101530144279587</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.24666369369971</v>
+        <v>1.298142360254281</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.67966707182512</v>
+        <v>-11.59386929423417</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.510469077592648</v>
+        <v>-1.476149966556268</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.249340619058962</v>
+        <v>-3.16354284146801</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.212149804015771</v>
+        <v>1.263628470570342</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.62765155785631</v>
+        <v>-11.54185378026536</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.485672536318722</v>
+        <v>-1.451353425282341</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.249340619058962</v>
+        <v>-3.16354284146801</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.216140139702172</v>
+        <v>1.267618806256742</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.76932339958043</v>
+        <v>-11.68352562198948</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.543816499907112</v>
+        <v>-1.509497388870731</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.249340619058962</v>
+        <v>-3.16354284146801</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.21466491280343</v>
+        <v>1.266143579358001</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.8682301400397</v>
+        <v>-11.78243236244875</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.568325785925949</v>
+        <v>-1.534006674889569</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.348247359518238</v>
+        <v>-3.262449581927286</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.170374278692737</v>
+        <v>1.221852945247308</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.6690780328026</v>
+        <v>-11.58328025521165</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.501716076677793</v>
+        <v>-1.467396965641413</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.182924833568424</v>
+        <v>-3.097127055977472</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.256516660615942</v>
+        <v>1.307995327170513</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.44323288008319</v>
+        <v>-11.35743510249224</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.401798942553821</v>
+        <v>-1.36747983151744</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.140998157981261</v>
+        <v>-3.055200380390309</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.291251739004449</v>
+        <v>1.34273040555902</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.1569580677605</v>
+        <v>-11.07116029016955</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.286149873068684</v>
+        <v>-1.251830762032303</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.140998157981261</v>
+        <v>-3.055200380390309</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.292390883560508</v>
+        <v>1.343869550115079</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.20985335580479</v>
+        <v>-11.12405557821383</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.30467421412429</v>
+        <v>-1.27035510308791</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.136042811892815</v>
+        <v>-3.050245034301863</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.297997865375683</v>
+        <v>1.349476531930254</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.92594462487604</v>
+        <v>-10.84014684728509</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.185377017514154</v>
+        <v>-1.151057906477774</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.136042811892815</v>
+        <v>-3.050245034301863</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.303731569614319</v>
+        <v>1.35521023616889</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.67895737468309</v>
+        <v>-10.59315959709213</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.096319379830839</v>
+        <v>-1.062000268794458</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.889055561699863</v>
+        <v>-2.803257784108911</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.442186657336225</v>
+        <v>1.493665323890796</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.41512050747902</v>
+        <v>-10.32932272988806</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.000668114262119</v>
+        <v>-0.9663490032257385</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.889055561699863</v>
+        <v>-2.803257784108911</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.432303176023318</v>
+        <v>1.483781842577889</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.14787870661062</v>
+        <v>-10.06208092901967</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8956059544141328</v>
+        <v>-0.8612868433777527</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.889055561699863</v>
+        <v>-2.803257784108911</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.430468615523944</v>
+        <v>1.481947282078515</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.872069543210133</v>
+        <v>-9.786271765619182</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7855826040273999</v>
+        <v>-0.7512634929910198</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.800036253421129</v>
+        <v>-2.714238475830177</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.483579885517723</v>
+        <v>1.535058552072295</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.848116002234175</v>
+        <v>-9.762318224643224</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7753326814915233</v>
+        <v>-0.7410135704551428</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.776082712445171</v>
+        <v>-2.690284934854219</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.498620516248791</v>
+        <v>1.550099182803363</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.584056063911378</v>
+        <v>-9.498258286320427</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6829690223241567</v>
+        <v>-0.6486499112877762</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.512022774122376</v>
+        <v>-2.426224996531424</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.643796163080717</v>
+        <v>1.695274829635288</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.876976440406541</v>
+        <v>-8.791178662815589</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4029242065825227</v>
+        <v>-0.3686050955461422</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.512022774122376</v>
+        <v>-2.426224996531424</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.641009129420416</v>
+        <v>1.692487795974987</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.83679214204035</v>
+        <v>-8.750994364449399</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3865068633482052</v>
+        <v>-0.3521877523118246</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.471838475756185</v>
+        <v>-2.386040698165233</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.665463332327972</v>
+        <v>1.716941998882543</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.756722346502546</v>
+        <v>-8.670924568911595</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3551121239123263</v>
+        <v>-0.3207930128759457</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.391768680218381</v>
+        <v>-2.305970902627429</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.712872030871411</v>
+        <v>1.764350697425982</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.78732685376181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.523241124272946</v>
+        <v>-8.437443346681995</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2537952061826343</v>
+        <v>-0.2194760951462538</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.158287457988782</v>
+        <v>-2.07248968039783</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.860885193047023</v>
+        <v>1.912363859601594</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.343532594129073</v>
+        <v>-8.257734816538122</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1848040044380439</v>
+        <v>-0.1504848934016634</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.101115953826086</v>
+        <v>-2.015318176235134</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.892295885231681</v>
+        <v>1.943774551786253</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.211257120498185</v>
+        <v>-8.125459342907234</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.136526328238662</v>
+        <v>-0.1022072172022814</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.9688404801952</v>
+        <v>-1.883042702604248</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.96702865615724</v>
+        <v>2.018507322711812</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575955</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.020657445825032</v>
+        <v>-7.934859668234082</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.05747139768176401</v>
+        <v>-0.02315228664538393</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.778240805522047</v>
+        <v>-1.692443027931095</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.084203521648768</v>
+        <v>2.13568218820334</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.75387899643099</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.771657647141451</v>
+        <v>-7.685859869550501</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.05503486301532723</v>
+        <v>0.08935397405170731</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.778240805522047</v>
+        <v>-1.692443027931095</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.097109862872427</v>
+        <v>2.148588529426998</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077647</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.877247636914555</v>
+        <v>-7.791449859323605</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1151770624931334</v>
+        <v>-0.08085795145675334</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.883830795295151</v>
+        <v>-1.798033017704199</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.905779939409346</v>
+        <v>1.957258605963917</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457905</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.895982539033152</v>
+        <v>-7.810184761442202</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.07412668146348578</v>
+        <v>-0.0398075704271057</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.883830795295151</v>
+        <v>-1.798033017704199</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.954324281286432</v>
+        <v>2.005802947841004</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180811</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.61924436436234</v>
+        <v>-7.53344658677139</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.03994760039083411</v>
+        <v>0.07426671142721375</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.702014134185225</v>
+        <v>-1.616216356594273</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.066793289938382</v>
+        <v>2.118271956492954</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879204</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.492351957927269</v>
+        <v>-7.40655418033632</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.08199057671138421</v>
+        <v>0.1163096877477638</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.575121727750155</v>
+        <v>-1.489323950159203</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.134214747545946</v>
+        <v>2.185693414100517</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568108</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.304764450017343</v>
+        <v>-7.218966672426394</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.1500649677802612</v>
+        <v>0.1843840788166413</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.575121727750155</v>
+        <v>-1.489323950159203</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.127254135450853</v>
+        <v>2.178732802005424</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.78291895796342</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.062616056563485</v>
+        <v>-6.976818278972535</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.2613866795429476</v>
+        <v>0.2957057905793277</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.575121727750155</v>
+        <v>-1.489323950159203</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.141716489831996</v>
+        <v>2.193195156386567</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.999386684795136</v>
+        <v>-6.913588907204187</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.281210548709482</v>
+        <v>0.3155296597458617</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.575121727750155</v>
+        <v>-1.489323950159203</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.136248610291191</v>
+        <v>2.187727276845762</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262049</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.81289899241813</v>
+        <v>-6.727101214827181</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.3533037196708615</v>
+        <v>0.3876228307072411</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.388634035373149</v>
+        <v>-1.302836257782197</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.245639319727972</v>
+        <v>2.297117986282543</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389911</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.791749793514687</v>
+        <v>-6.705952015923738</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.3694643774695643</v>
+        <v>0.4037834885059439</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.367484836469706</v>
+        <v>-1.281687058878754</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.266029817307363</v>
+        <v>2.317508483861935</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788095</v>
+        <v>3.748324832788096</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.547984351531243</v>
+        <v>-6.462186573940293</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.4627512626099928</v>
+        <v>0.4970703736463724</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.367484836469706</v>
+        <v>-1.281687058878754</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.261810525654414</v>
+        <v>2.313289192208985</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527526</v>
+        <v>3.824307657527528</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.283956284337982</v>
+        <v>-6.198158506747033</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5704868034073129</v>
+        <v>0.6048059144436926</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.165619437653752</v>
+        <v>-1.0798216600628</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.385054078864002</v>
+        <v>2.436532745418573</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749185</v>
+        <v>3.826351398749186</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.034105890388908</v>
+        <v>-5.948308112797958</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.663169035970645</v>
+        <v>0.6974881470070247</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.165619437653752</v>
+        <v>-1.0798216600628</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.377796153847704</v>
+        <v>2.429274820402275</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481498</v>
+        <v>3.8359544114815</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.730538401384929</v>
+        <v>-5.64474062379398</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7881951550928852</v>
+        <v>0.8225142661292648</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.165619437653752</v>
+        <v>-1.0798216600628</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.381395277368353</v>
+        <v>2.432873943922924</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862987</v>
+        <v>3.780930335862989</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.657058492532915</v>
+        <v>-5.571260714941966</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8309146246882446</v>
+        <v>0.8652337357246243</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.092139528801738</v>
+        <v>-1.006341751210786</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.438810728734115</v>
+        <v>2.490289395288686</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102782</v>
+        <v>3.773761647102784</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.432025492864092</v>
+        <v>-5.346227715273143</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9199483021720707</v>
+        <v>0.9542674132084503</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8671065291329151</v>
+        <v>-0.7813087515419631</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.572851006151706</v>
+        <v>2.624329672706277</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353077</v>
+        <v>3.764614304353079</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.217391115227685</v>
+        <v>-5.131593337636736</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.010496854280951</v>
+        <v>1.04481596531733</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.6524721514965083</v>
+        <v>-0.5666743739055563</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.706326433787868</v>
+        <v>2.757805100342439</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544785</v>
+        <v>3.798811195544786</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.950790758253333</v>
+        <v>-4.864992980662384</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.098331255854487</v>
+        <v>1.132650366890867</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.6524721514965083</v>
+        <v>-0.5666743739055563</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.687520692571663</v>
+        <v>2.738999359126234</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712296</v>
+        <v>3.797691308712298</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.710360261448473</v>
+        <v>-4.624562483857524</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.196246531201309</v>
+        <v>1.230565642237688</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.412041654691648</v>
+        <v>-0.326243877100696</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.833522067279457</v>
+        <v>2.885000733834028</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837688</v>
+        <v>3.821589933837689</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.467569453799028</v>
+        <v>-4.381771676208079</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.297292168095907</v>
+        <v>1.331611279132287</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.412041654691648</v>
+        <v>-0.326243877100696</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.837451381114277</v>
+        <v>2.888930047668848</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349969</v>
+        <v>3.822323422349971</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.227964362191939</v>
+        <v>-4.142166584600989</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.393812788656082</v>
+        <v>1.428131899692462</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.3449937070231535</v>
+        <v>-0.2591959294322015</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.878358733632714</v>
+        <v>2.929837400187285</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972343</v>
+        <v>3.848613050972345</v>
       </c>
       <c r="C1928" t="n">
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-3.985308773768776</v>
+        <v>-3.899510996177826</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.487873095245341</v>
+        <v>1.522192206281721</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.3449937070231535</v>
+        <v>-0.2591959294322015</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.875356804852707</v>
+        <v>2.926835471407278</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145943</v>
+        <v>3.818665376145945</v>
       </c>
       <c r="C1929" t="n">
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.765287975731765</v>
+        <v>-3.679490198140815</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.57746045147076</v>
+        <v>1.61177956250714</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2037738619551732</v>
+        <v>-0.1179760843642212</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.961667748904109</v>
+        <v>3.013146415458681</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.56768974600297</v>
+        <v>3.875385691262985</v>
       </c>
       <c r="C1930" t="n">
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.563076551463589</v>
+        <v>-3.480241568236006</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.674239203979853</v>
+        <v>1.707373197270887</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2037738619551732</v>
+        <v>-0.1179760843642212</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.977561931705933</v>
+        <v>3.029040598260504</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240411.xlsx
+++ b/tame_output/ON/bt/strategyON_20240411.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -615,11 +615,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.4%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>8.9%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.0%</t>
+          <t>-77.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.6%</t>
+          <t>117.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.5%</t>
+          <t>136.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,11 +973,11 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-685.6%</t>
+          <t>-685.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-55.3%</t>
+          <t>-55.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.4%</t>
+          <t>-73.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-509.6%</t>
+          <t>-529.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,11 +1131,11 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-268.8%</t>
+          <t>-268.7%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>129.2%</t>
+          <t>136.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-205.5%</t>
+          <t>-213.3%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-19.1%</t>
+          <t>-19.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-158.3%</t>
+          <t>-158.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-235.8%</t>
+          <t>-235.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-143.1%</t>
+          <t>-126.2%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1930"/>
+  <dimension ref="A1:G1931"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.153375272995</v>
+        <v>-10.15087183927061</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.9328349453184841</v>
+        <v>-0.9318335718287263</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.313527906130268</v>
+        <v>-2.311024472405875</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.740754844515103</v>
+        <v>1.742256904749739</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.14689912620144</v>
+        <v>-10.14439569247705</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.9272027359792916</v>
+        <v>-0.9262013624895338</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.307051759336709</v>
+        <v>-2.304548325612315</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.747682283213008</v>
+        <v>1.749184343447644</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.14320820124503</v>
+        <v>-10.14070476752064</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.9257263659967276</v>
+        <v>-0.9247249925069698</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.307051759336709</v>
+        <v>-2.304548325612315</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.747682283213008</v>
+        <v>1.749184343447644</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.34746637657489</v>
+        <v>-10.3449629428505</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.001916439010031</v>
+        <v>-1.000915065520273</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.434690703950698</v>
+        <v>-2.432187270226304</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.676612113563257</v>
+        <v>1.678114173797893</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.50810540306326</v>
+        <v>-10.50560196933887</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.061689495120941</v>
+        <v>-1.060688121631183</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.549424176953093</v>
+        <v>-2.5469207432287</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.612254584246255</v>
+        <v>1.613756644480892</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.43463557139581</v>
+        <v>-10.43213213767142</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.01692986096054</v>
+        <v>-1.015928487470782</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.475954345285645</v>
+        <v>-2.473450911561251</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.671708184740145</v>
+        <v>1.673210244974782</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.60975998878235</v>
+        <v>-10.60725655505796</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.07242440716764</v>
+        <v>-1.071423033677883</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.651078762672189</v>
+        <v>-2.648575328947795</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.581188755055736</v>
+        <v>1.582690815290372</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.84421208279684</v>
+        <v>-10.84170864907245</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.173424409675032</v>
+        <v>-1.172423036185274</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.651078762672189</v>
+        <v>-2.648575328947795</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.57396959015414</v>
+        <v>1.575471650388776</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.13201592733408</v>
+        <v>-11.12951249360969</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.295218138263904</v>
+        <v>-1.294216764774146</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.938882607209427</v>
+        <v>-2.936379173485033</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.394615092657821</v>
+        <v>1.396117152892457</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.36184037449791</v>
+        <v>-11.35933694077351</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.386032127290878</v>
+        <v>-1.38503075380112</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.101530144279587</v>
+        <v>-3.099026710555194</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.298142360254281</v>
+        <v>1.299644420488917</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.59386929423417</v>
+        <v>-11.59136586050978</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.476149966556268</v>
+        <v>-1.47514859306651</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.16354284146801</v>
+        <v>-3.161039407743617</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.263628470570342</v>
+        <v>1.265130530804978</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.54185378026536</v>
+        <v>-11.53935034654096</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.451353425282341</v>
+        <v>-1.450352051792584</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.16354284146801</v>
+        <v>-3.161039407743617</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.267618806256742</v>
+        <v>1.269120866491379</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.68352562198948</v>
+        <v>-11.68102218826508</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.509497388870731</v>
+        <v>-1.508496015380974</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.16354284146801</v>
+        <v>-3.161039407743617</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.266143579358001</v>
+        <v>1.267645639592637</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.78243236244875</v>
+        <v>-11.77992892872436</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.534006674889569</v>
+        <v>-1.533005301399812</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.262449581927286</v>
+        <v>-3.259946148202892</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.221852945247308</v>
+        <v>1.223355005481944</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.58328025521165</v>
+        <v>-11.58077682148726</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.467396965641413</v>
+        <v>-1.466395592151655</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.097127055977472</v>
+        <v>-3.094623622253079</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.307995327170513</v>
+        <v>1.309497387405149</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.35743510249224</v>
+        <v>-11.35493166876785</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.36747983151744</v>
+        <v>-1.366478458027682</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.055200380390309</v>
+        <v>-3.052696946665916</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.34273040555902</v>
+        <v>1.344232465793656</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.07116029016955</v>
+        <v>-11.06865685644515</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.251830762032303</v>
+        <v>-1.250829388542545</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.055200380390309</v>
+        <v>-3.052696946665916</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.343869550115079</v>
+        <v>1.345371610349715</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.12405557821383</v>
+        <v>-11.12155214448944</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.27035510308791</v>
+        <v>-1.269353729598151</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.050245034301863</v>
+        <v>-3.047741600577469</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.349476531930254</v>
+        <v>1.35097859216489</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.84014684728509</v>
+        <v>-10.83764341356069</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.151057906477774</v>
+        <v>-1.150056532988016</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.050245034301863</v>
+        <v>-3.047741600577469</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.35521023616889</v>
+        <v>1.356712296403527</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.59315959709213</v>
+        <v>-10.59065616336774</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.062000268794458</v>
+        <v>-1.0609988953047</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.803257784108911</v>
+        <v>-2.800754350384517</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.493665323890796</v>
+        <v>1.495167384125432</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.32932272988806</v>
+        <v>-10.32681929616367</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9663490032257385</v>
+        <v>-0.9653476297359798</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.803257784108911</v>
+        <v>-2.800754350384517</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.483781842577889</v>
+        <v>1.485283902812525</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.06208092901967</v>
+        <v>-10.05957749529527</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8612868433777527</v>
+        <v>-0.860285469887994</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.803257784108911</v>
+        <v>-2.800754350384517</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.481947282078515</v>
+        <v>1.483449342313151</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.786271765619182</v>
+        <v>-9.783768331894786</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7512634929910198</v>
+        <v>-0.7502621195012611</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.714238475830177</v>
+        <v>-2.711735042105784</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.535058552072295</v>
+        <v>1.53656061230693</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.762318224643224</v>
+        <v>-9.759814790918828</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7410135704551428</v>
+        <v>-0.7400121969653846</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.690284934854219</v>
+        <v>-2.687781501129826</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.550099182803363</v>
+        <v>1.551601243037999</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.498258286320427</v>
+        <v>-9.495754852596031</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6486499112877762</v>
+        <v>-0.6476485377980179</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.426224996531424</v>
+        <v>-2.42372156280703</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.695274829635288</v>
+        <v>1.696776889869924</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.791178662815589</v>
+        <v>-8.788675229091194</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3686050955461422</v>
+        <v>-0.3676037220563839</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.426224996531424</v>
+        <v>-2.42372156280703</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.692487795974987</v>
+        <v>1.693989856209623</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.750994364449399</v>
+        <v>-8.748490930725003</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3521877523118246</v>
+        <v>-0.3511863788220664</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.386040698165233</v>
+        <v>-2.383537264440839</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.716941998882543</v>
+        <v>1.718444059117179</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.670924568911595</v>
+        <v>-8.668421135187199</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3207930128759457</v>
+        <v>-0.3197916393861875</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.305970902627429</v>
+        <v>-2.303467468903035</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.764350697425982</v>
+        <v>1.765852757660618</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78732685376181</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.437443346681995</v>
+        <v>-8.434939912957599</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2194760951462538</v>
+        <v>-0.2184747216564955</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.07248968039783</v>
+        <v>-2.069986246673437</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.912363859601594</v>
+        <v>1.91386591983623</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.257734816538122</v>
+        <v>-8.255231382813726</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1504848934016634</v>
+        <v>-0.1494835199119051</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.015318176235134</v>
+        <v>-2.012814742510741</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.943774551786253</v>
+        <v>1.945276612020888</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860429</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.125459342907234</v>
+        <v>-8.122955909182838</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1022072172022814</v>
+        <v>-0.1012058437125232</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.883042702604248</v>
+        <v>-1.880539268879854</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.018507322711812</v>
+        <v>2.020009382946447</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575955</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.934859668234082</v>
+        <v>-7.932356234509686</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.02315228664538393</v>
+        <v>-0.02215091315562567</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.692443027931095</v>
+        <v>-1.689939594206701</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.13568218820334</v>
+        <v>2.137184248437975</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.75387899643099</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.685859869550501</v>
+        <v>-7.683356435826105</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.08935397405170731</v>
+        <v>0.09035534754146557</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.692443027931095</v>
+        <v>-1.689939594206701</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.148588529426998</v>
+        <v>2.150090589661635</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077647</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.791449859323605</v>
+        <v>-7.788946425599209</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.08085795145675334</v>
+        <v>-0.07985657796699464</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.798033017704199</v>
+        <v>-1.795529583979806</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.957258605963917</v>
+        <v>1.958760666198553</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457905</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.810184761442202</v>
+        <v>-7.807681327717806</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.0398075704271057</v>
+        <v>-0.03880619693734744</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.798033017704199</v>
+        <v>-1.795529583979806</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.005802947841004</v>
+        <v>2.007305008075639</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180811</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.53344658677139</v>
+        <v>-7.530943153046994</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.07426671142721375</v>
+        <v>0.07526808491697201</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.616216356594273</v>
+        <v>-1.61371292286988</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.118271956492954</v>
+        <v>2.11977401672759</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879204</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.40655418033632</v>
+        <v>-7.404050746611924</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.1163096877477638</v>
+        <v>0.1173110612375221</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.489323950159203</v>
+        <v>-1.48682051643481</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.185693414100517</v>
+        <v>2.187195474335153</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568108</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.218966672426394</v>
+        <v>-7.216463238701998</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.1843840788166413</v>
+        <v>0.1853854523063996</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.489323950159203</v>
+        <v>-1.48682051643481</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.178732802005424</v>
+        <v>2.18023486224006</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78291895796342</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.976818278972535</v>
+        <v>-6.97431484524814</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.2957057905793277</v>
+        <v>0.2967071640690859</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.489323950159203</v>
+        <v>-1.48682051643481</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.193195156386567</v>
+        <v>2.194697216621203</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.913588907204187</v>
+        <v>-6.911085473479791</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3155296597458617</v>
+        <v>0.3165310332356204</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.489323950159203</v>
+        <v>-1.48682051643481</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.187727276845762</v>
+        <v>2.189229337080398</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262049</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.727101214827181</v>
+        <v>-6.724597781102785</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.3876228307072411</v>
+        <v>0.3886242041969994</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.302836257782197</v>
+        <v>-1.300332824057804</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.297117986282543</v>
+        <v>2.298620046517179</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389911</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.705952015923738</v>
+        <v>-6.703448582199342</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4037834885059439</v>
+        <v>0.4047848619957026</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.281687058878754</v>
+        <v>-1.279183625154361</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.317508483861935</v>
+        <v>2.31901054409657</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788096</v>
+        <v>3.748324832788095</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.462186573940293</v>
+        <v>-6.459683140215898</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.4970703736463724</v>
+        <v>0.4980717471361307</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.281687058878754</v>
+        <v>-1.279183625154361</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.313289192208985</v>
+        <v>2.314791252443621</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527528</v>
+        <v>3.824307657527526</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.198158506747033</v>
+        <v>-6.195655073022637</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6048059144436926</v>
+        <v>0.6058072879334508</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.0798216600628</v>
+        <v>-1.077318226338407</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.436532745418573</v>
+        <v>2.438034805653209</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749186</v>
+        <v>3.826351398749185</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.948308112797958</v>
+        <v>-5.945804679073563</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6974881470070247</v>
+        <v>0.6984895204967829</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.0798216600628</v>
+        <v>-1.077318226338407</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.429274820402275</v>
+        <v>2.430776880636912</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.8359544114815</v>
+        <v>3.835954411481498</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.64474062379398</v>
+        <v>-5.642237190069584</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8225142661292648</v>
+        <v>0.8235156396190235</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.0798216600628</v>
+        <v>-1.077318226338407</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.432873943922924</v>
+        <v>2.43437600415756</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862989</v>
+        <v>3.780930335862987</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.571260714941966</v>
+        <v>-5.56875728121757</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8652337357246243</v>
+        <v>0.8662351092143825</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.006341751210786</v>
+        <v>-1.003838317486393</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.490289395288686</v>
+        <v>2.491791455523322</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102784</v>
+        <v>3.773761647102782</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.346227715273143</v>
+        <v>-5.343724281548747</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9542674132084503</v>
+        <v>0.9552687866982086</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.7813087515419631</v>
+        <v>-0.7788053178175699</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.624329672706277</v>
+        <v>2.625831732940913</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353079</v>
+        <v>3.764614304353077</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.131593337636736</v>
+        <v>-5.12908990391234</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.04481596531733</v>
+        <v>1.045817338807089</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.5666743739055563</v>
+        <v>-0.5641709401811631</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.757805100342439</v>
+        <v>2.759307160577074</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544786</v>
+        <v>3.798811195544785</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.864992980662384</v>
+        <v>-4.862489546937988</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.132650366890867</v>
+        <v>1.133651740380625</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.5666743739055563</v>
+        <v>-0.5641709401811631</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.738999359126234</v>
+        <v>2.74050141936087</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712298</v>
+        <v>3.797691308712296</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.624562483857524</v>
+        <v>-4.622059050133128</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.230565642237688</v>
+        <v>1.231567015727447</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.326243877100696</v>
+        <v>-0.3237404433763028</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.885000733834028</v>
+        <v>2.886502794068664</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837689</v>
+        <v>3.821589933837688</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.381771676208079</v>
+        <v>-4.379268242483683</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.331611279132287</v>
+        <v>1.332612652622045</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.326243877100696</v>
+        <v>-0.3237404433763028</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.888930047668848</v>
+        <v>2.890432107903484</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349971</v>
+        <v>3.822323422349969</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.142166584600989</v>
+        <v>-4.139663150876594</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.428131899692462</v>
+        <v>1.429133273182221</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.2591959294322015</v>
+        <v>-0.2566924957078083</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.929837400187285</v>
+        <v>2.931339460421921</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972345</v>
+        <v>3.848613050972343</v>
       </c>
       <c r="C1928" t="n">
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-3.899510996177826</v>
+        <v>-3.89700756245343</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.522192206281721</v>
+        <v>1.523193579771479</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.2591959294322015</v>
+        <v>-0.2566924957078083</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.926835471407278</v>
+        <v>2.928337531641914</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145945</v>
+        <v>3.818665376145943</v>
       </c>
       <c r="C1929" t="n">
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.679490198140815</v>
+        <v>-3.676986764416419</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.61177956250714</v>
+        <v>1.612780935996898</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.1179760843642212</v>
+        <v>-0.115472650639828</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.013146415458681</v>
+        <v>3.014648475693317</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,45 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.875385691262985</v>
+        <v>3.843270952009954</v>
       </c>
       <c r="C1930" t="n">
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.480241568236006</v>
+        <v>-3.675627195070525</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.707373197270887</v>
+        <v>1.629218946537079</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.1179760843642212</v>
+        <v>-0.115472650639828</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.029040598260504</v>
+        <v>3.03054265849514</v>
+      </c>
+    </row>
+    <row r="1931">
+      <c r="A1931" s="2" t="n">
+        <v>45393</v>
+      </c>
+      <c r="B1931" t="n">
+        <v>3.874614466050415</v>
+      </c>
+      <c r="C1931" t="n">
+        <v>3.205223570616869</v>
+      </c>
+      <c r="D1931" t="n">
+        <v>-3.675627195070525</v>
+      </c>
+      <c r="E1931" t="n">
+        <v>1.629218946537079</v>
+      </c>
+      <c r="F1931" t="n">
+        <v>-0.115472650639828</v>
+      </c>
+      <c r="G1931" t="n">
+        <v>3.198287367603237</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240411.xlsx
+++ b/tame_output/ON/bt/strategyON_20240411.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.7%</t>
+          <t>-76.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.2%</t>
+          <t>117.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-685.3%</t>
+          <t>-685.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-55.2%</t>
+          <t>-55.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.2%</t>
+          <t>-72.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-529.1%</t>
+          <t>-509.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-268.7%</t>
+          <t>-268.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>136.0%</t>
+          <t>129.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-213.3%</t>
+          <t>-205.5%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-19.0%</t>
+          <t>-19.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-158.4%</t>
+          <t>-158.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-235.5%</t>
+          <t>-235.8%</t>
         </is>
       </c>
     </row>
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.15087183927061</v>
+        <v>-10.153375272995</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.9318335718287263</v>
+        <v>-0.9328349453184841</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.311024472405875</v>
+        <v>-2.313527906130268</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.742256904749739</v>
+        <v>1.740754844515103</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.14439569247705</v>
+        <v>-10.14689912620144</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.9262013624895338</v>
+        <v>-0.9272027359792916</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.304548325612315</v>
+        <v>-2.307051759336709</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.749184343447644</v>
+        <v>1.747682283213008</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.14070476752064</v>
+        <v>-10.14320820124503</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.9247249925069698</v>
+        <v>-0.9257263659967276</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.304548325612315</v>
+        <v>-2.307051759336709</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.749184343447644</v>
+        <v>1.747682283213008</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.3449629428505</v>
+        <v>-10.34746637657489</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.000915065520273</v>
+        <v>-1.001916439010031</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.432187270226304</v>
+        <v>-2.434690703950698</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.678114173797893</v>
+        <v>1.676612113563257</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.50560196933887</v>
+        <v>-10.50810540306326</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.060688121631183</v>
+        <v>-1.061689495120941</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.5469207432287</v>
+        <v>-2.549424176953093</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.613756644480892</v>
+        <v>1.612254584246255</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.43213213767142</v>
+        <v>-10.43463557139581</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.015928487470782</v>
+        <v>-1.01692986096054</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.473450911561251</v>
+        <v>-2.475954345285645</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.673210244974782</v>
+        <v>1.671708184740145</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.60725655505796</v>
+        <v>-10.60975998878235</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.071423033677883</v>
+        <v>-1.07242440716764</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.648575328947795</v>
+        <v>-2.651078762672189</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.582690815290372</v>
+        <v>1.581188755055736</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.84170864907245</v>
+        <v>-10.84421208279684</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.172423036185274</v>
+        <v>-1.173424409675032</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.648575328947795</v>
+        <v>-2.651078762672189</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.575471650388776</v>
+        <v>1.57396959015414</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.12951249360969</v>
+        <v>-11.13201592733408</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.294216764774146</v>
+        <v>-1.295218138263904</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.936379173485033</v>
+        <v>-2.938882607209427</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.396117152892457</v>
+        <v>1.394615092657821</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.35933694077351</v>
+        <v>-11.36184037449791</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.38503075380112</v>
+        <v>-1.386032127290878</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.099026710555194</v>
+        <v>-3.101530144279587</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.299644420488917</v>
+        <v>1.298142360254281</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.59136586050978</v>
+        <v>-11.59386929423417</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.47514859306651</v>
+        <v>-1.476149966556268</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.161039407743617</v>
+        <v>-3.16354284146801</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.265130530804978</v>
+        <v>1.263628470570342</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.53935034654096</v>
+        <v>-11.54185378026536</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.450352051792584</v>
+        <v>-1.451353425282341</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.161039407743617</v>
+        <v>-3.16354284146801</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.269120866491379</v>
+        <v>1.267618806256742</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.68102218826508</v>
+        <v>-11.68352562198948</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.508496015380974</v>
+        <v>-1.509497388870731</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.161039407743617</v>
+        <v>-3.16354284146801</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.267645639592637</v>
+        <v>1.266143579358001</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.77992892872436</v>
+        <v>-11.78243236244875</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.533005301399812</v>
+        <v>-1.534006674889569</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.259946148202892</v>
+        <v>-3.262449581927286</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.223355005481944</v>
+        <v>1.221852945247308</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.58077682148726</v>
+        <v>-11.58328025521165</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.466395592151655</v>
+        <v>-1.467396965641413</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.094623622253079</v>
+        <v>-3.097127055977472</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.309497387405149</v>
+        <v>1.307995327170513</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.35493166876785</v>
+        <v>-11.35743510249224</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.366478458027682</v>
+        <v>-1.36747983151744</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.052696946665916</v>
+        <v>-3.055200380390309</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.344232465793656</v>
+        <v>1.34273040555902</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.06865685644515</v>
+        <v>-11.07116029016955</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.250829388542545</v>
+        <v>-1.251830762032303</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.052696946665916</v>
+        <v>-3.055200380390309</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.345371610349715</v>
+        <v>1.343869550115079</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.12155214448944</v>
+        <v>-11.12405557821383</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.269353729598151</v>
+        <v>-1.27035510308791</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.047741600577469</v>
+        <v>-3.050245034301863</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.35097859216489</v>
+        <v>1.349476531930254</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.83764341356069</v>
+        <v>-10.84014684728509</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.150056532988016</v>
+        <v>-1.151057906477774</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.047741600577469</v>
+        <v>-3.050245034301863</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.356712296403527</v>
+        <v>1.35521023616889</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.59065616336774</v>
+        <v>-10.59315959709213</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.0609988953047</v>
+        <v>-1.062000268794458</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.800754350384517</v>
+        <v>-2.803257784108911</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.495167384125432</v>
+        <v>1.493665323890796</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.32681929616367</v>
+        <v>-10.32932272988806</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9653476297359798</v>
+        <v>-0.9663490032257385</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.800754350384517</v>
+        <v>-2.803257784108911</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.485283902812525</v>
+        <v>1.483781842577889</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.05957749529527</v>
+        <v>-10.06208092901967</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.860285469887994</v>
+        <v>-0.8612868433777527</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.800754350384517</v>
+        <v>-2.803257784108911</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.483449342313151</v>
+        <v>1.481947282078515</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.783768331894786</v>
+        <v>-9.786271765619182</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7502621195012611</v>
+        <v>-0.7512634929910198</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.711735042105784</v>
+        <v>-2.714238475830177</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.53656061230693</v>
+        <v>1.535058552072295</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.759814790918828</v>
+        <v>-9.762318224643224</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7400121969653846</v>
+        <v>-0.7410135704551428</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.687781501129826</v>
+        <v>-2.690284934854219</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.551601243037999</v>
+        <v>1.550099182803363</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.495754852596031</v>
+        <v>-9.498258286320427</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6476485377980179</v>
+        <v>-0.6486499112877762</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.42372156280703</v>
+        <v>-2.426224996531424</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.696776889869924</v>
+        <v>1.695274829635288</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.788675229091194</v>
+        <v>-8.791178662815589</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3676037220563839</v>
+        <v>-0.3686050955461422</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.42372156280703</v>
+        <v>-2.426224996531424</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.693989856209623</v>
+        <v>1.692487795974987</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.748490930725003</v>
+        <v>-8.750994364449399</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3511863788220664</v>
+        <v>-0.3521877523118246</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.383537264440839</v>
+        <v>-2.386040698165233</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.718444059117179</v>
+        <v>1.716941998882543</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.668421135187199</v>
+        <v>-8.670924568911595</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3197916393861875</v>
+        <v>-0.3207930128759457</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.303467468903035</v>
+        <v>-2.305970902627429</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.765852757660618</v>
+        <v>1.764350697425982</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.78732685376181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.434939912957599</v>
+        <v>-8.437443346681995</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2184747216564955</v>
+        <v>-0.2194760951462538</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.069986246673437</v>
+        <v>-2.07248968039783</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.91386591983623</v>
+        <v>1.912363859601594</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.255231382813726</v>
+        <v>-8.257734816538122</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1494835199119051</v>
+        <v>-0.1504848934016634</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.012814742510741</v>
+        <v>-2.015318176235134</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.945276612020888</v>
+        <v>1.943774551786253</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.122955909182838</v>
+        <v>-8.125459342907234</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1012058437125232</v>
+        <v>-0.1022072172022814</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.880539268879854</v>
+        <v>-1.883042702604248</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.020009382946447</v>
+        <v>2.018507322711812</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575955</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.932356234509686</v>
+        <v>-7.934859668234082</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.02215091315562567</v>
+        <v>-0.02315228664538393</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.689939594206701</v>
+        <v>-1.692443027931095</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.137184248437975</v>
+        <v>2.13568218820334</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.75387899643099</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.683356435826105</v>
+        <v>-7.685859869550501</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.09035534754146557</v>
+        <v>0.08935397405170731</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.689939594206701</v>
+        <v>-1.692443027931095</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.150090589661635</v>
+        <v>2.148588529426998</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077647</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.788946425599209</v>
+        <v>-7.791449859323605</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.07985657796699464</v>
+        <v>-0.08085795145675334</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.795529583979806</v>
+        <v>-1.798033017704199</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.958760666198553</v>
+        <v>1.957258605963917</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457905</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.807681327717806</v>
+        <v>-7.810184761442202</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.03880619693734744</v>
+        <v>-0.0398075704271057</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.795529583979806</v>
+        <v>-1.798033017704199</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.007305008075639</v>
+        <v>2.005802947841004</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180811</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.530943153046994</v>
+        <v>-7.53344658677139</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.07526808491697201</v>
+        <v>0.07426671142721375</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.61371292286988</v>
+        <v>-1.616216356594273</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.11977401672759</v>
+        <v>2.118271956492954</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879204</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.404050746611924</v>
+        <v>-7.40655418033632</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.1173110612375221</v>
+        <v>0.1163096877477638</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.48682051643481</v>
+        <v>-1.489323950159203</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.187195474335153</v>
+        <v>2.185693414100517</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568108</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.216463238701998</v>
+        <v>-7.218966672426394</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.1853854523063996</v>
+        <v>0.1843840788166413</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.48682051643481</v>
+        <v>-1.489323950159203</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.18023486224006</v>
+        <v>2.178732802005424</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.78291895796342</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.97431484524814</v>
+        <v>-6.976818278972535</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.2967071640690859</v>
+        <v>0.2957057905793277</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.48682051643481</v>
+        <v>-1.489323950159203</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.194697216621203</v>
+        <v>2.193195156386567</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.911085473479791</v>
+        <v>-6.913588907204187</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3165310332356204</v>
+        <v>0.3155296597458617</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.48682051643481</v>
+        <v>-1.489323950159203</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.189229337080398</v>
+        <v>2.187727276845762</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262049</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.724597781102785</v>
+        <v>-6.727101214827181</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.3886242041969994</v>
+        <v>0.3876228307072411</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.300332824057804</v>
+        <v>-1.302836257782197</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.298620046517179</v>
+        <v>2.297117986282543</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389911</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.703448582199342</v>
+        <v>-6.705952015923738</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4047848619957026</v>
+        <v>0.4037834885059439</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.279183625154361</v>
+        <v>-1.281687058878754</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.31901054409657</v>
+        <v>2.317508483861935</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788095</v>
+        <v>3.748324832788096</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.459683140215898</v>
+        <v>-6.462186573940293</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.4980717471361307</v>
+        <v>0.4970703736463724</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.279183625154361</v>
+        <v>-1.281687058878754</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.314791252443621</v>
+        <v>2.313289192208985</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527526</v>
+        <v>3.824307657527528</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.195655073022637</v>
+        <v>-6.198158506747033</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6058072879334508</v>
+        <v>0.6048059144436926</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.077318226338407</v>
+        <v>-1.0798216600628</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.438034805653209</v>
+        <v>2.436532745418573</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749185</v>
+        <v>3.826351398749186</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.945804679073563</v>
+        <v>-5.948308112797958</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6984895204967829</v>
+        <v>0.6974881470070247</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.077318226338407</v>
+        <v>-1.0798216600628</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.430776880636912</v>
+        <v>2.429274820402275</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481498</v>
+        <v>3.8359544114815</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.642237190069584</v>
+        <v>-5.64474062379398</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8235156396190235</v>
+        <v>0.8225142661292648</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.077318226338407</v>
+        <v>-1.0798216600628</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.43437600415756</v>
+        <v>2.432873943922924</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862987</v>
+        <v>3.780930335862989</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.56875728121757</v>
+        <v>-5.571260714941966</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8662351092143825</v>
+        <v>0.8652337357246243</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.003838317486393</v>
+        <v>-1.006341751210786</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.491791455523322</v>
+        <v>2.490289395288686</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102782</v>
+        <v>3.773761647102784</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.343724281548747</v>
+        <v>-5.346227715273143</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9552687866982086</v>
+        <v>0.9542674132084503</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.7788053178175699</v>
+        <v>-0.7813087515419631</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.625831732940913</v>
+        <v>2.624329672706277</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353077</v>
+        <v>3.764614304353079</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.12908990391234</v>
+        <v>-5.131593337636736</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.045817338807089</v>
+        <v>1.04481596531733</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.5641709401811631</v>
+        <v>-0.5666743739055563</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.759307160577074</v>
+        <v>2.757805100342439</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544785</v>
+        <v>3.798811195544786</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.862489546937988</v>
+        <v>-4.864992980662384</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.133651740380625</v>
+        <v>1.132650366890867</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.5641709401811631</v>
+        <v>-0.5666743739055563</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.74050141936087</v>
+        <v>2.738999359126234</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712296</v>
+        <v>3.797691308712298</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.622059050133128</v>
+        <v>-4.624562483857524</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.231567015727447</v>
+        <v>1.230565642237688</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.3237404433763028</v>
+        <v>-0.326243877100696</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.886502794068664</v>
+        <v>2.885000733834028</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837688</v>
+        <v>3.821589933837689</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.379268242483683</v>
+        <v>-4.381771676208079</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.332612652622045</v>
+        <v>1.331611279132287</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.3237404433763028</v>
+        <v>-0.326243877100696</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.890432107903484</v>
+        <v>2.888930047668848</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349969</v>
+        <v>3.822323422349971</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.139663150876594</v>
+        <v>-4.142166584600989</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.429133273182221</v>
+        <v>1.428131899692462</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.2566924957078083</v>
+        <v>-0.2591959294322015</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.931339460421921</v>
+        <v>2.929837400187285</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972343</v>
+        <v>3.848613050972345</v>
       </c>
       <c r="C1928" t="n">
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-3.89700756245343</v>
+        <v>-3.899510996177826</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.523193579771479</v>
+        <v>1.522192206281721</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.2566924957078083</v>
+        <v>-0.2591959294322015</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.928337531641914</v>
+        <v>2.926835471407278</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145943</v>
+        <v>3.818665376145945</v>
       </c>
       <c r="C1929" t="n">
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.676986764416419</v>
+        <v>-3.679490198140815</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.612780935996898</v>
+        <v>1.61177956250714</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.115472650639828</v>
+        <v>-0.1179760843642212</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.014648475693317</v>
+        <v>3.013146415458681</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009954</v>
+        <v>3.843270952009957</v>
       </c>
       <c r="C1930" t="n">
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.675627195070525</v>
+        <v>-3.480241568236006</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.629218946537079</v>
+        <v>1.707373197270887</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.115472650639828</v>
+        <v>-0.1179760843642212</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.03054265849514</v>
+        <v>3.029040598260504</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,19 +45958,19 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.874614466050415</v>
+        <v>3.874614466050418</v>
       </c>
       <c r="C1931" t="n">
         <v>3.205223570616869</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.675627195070525</v>
+        <v>-3.480241568236006</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.629218946537079</v>
+        <v>1.707373197270887</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.115472650639828</v>
+        <v>-0.1179760843642212</v>
       </c>
       <c r="G1931" t="n">
         <v>3.198287367603237</v>

--- a/tame_output/ON/bt/strategyON_20240411.xlsx
+++ b/tame_output/ON/bt/strategyON_20240411.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>29.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>-1.5%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.9%</t>
+          <t>-78.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.6%</t>
+          <t>117.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.4%</t>
+          <t>137.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-685.6%</t>
+          <t>-708.1%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-55.3%</t>
+          <t>-56.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.4%</t>
+          <t>-74.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>97.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>501.7%</t>
+          <t>499.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-509.6%</t>
+          <t>-541.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-268.8%</t>
+          <t>-277.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-43.2%</t>
+          <t>-43.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>129.2%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-205.5%</t>
+          <t>-218.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-26.6%</t>
+          <t>-30.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-35.5%</t>
+          <t>-36.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-19.1%</t>
+          <t>-22.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-158.3%</t>
+          <t>-152.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-235.8%</t>
+          <t>-259.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-30.6%</t>
+          <t>-31.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-126.2%</t>
+          <t>-157.1%</t>
         </is>
       </c>
     </row>
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776682</v>
+        <v>3.500446096776683</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.14689912620144</v>
+        <v>-10.37224929355527</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.9272027359792916</v>
+        <v>-1.017342802920821</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.307051759336709</v>
+        <v>-2.532401926690532</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.747682283213008</v>
+        <v>1.612472182800714</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.14320820124503</v>
+        <v>-10.36855836859885</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.9257263659967276</v>
+        <v>-1.015866432938257</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.307051759336709</v>
+        <v>-2.532401926690532</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.747682283213008</v>
+        <v>1.612472182800714</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.34746637657489</v>
+        <v>-10.57281654392872</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.001916439010031</v>
+        <v>-1.09205650595156</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.434690703950698</v>
+        <v>-2.660040871304521</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.676612113563257</v>
+        <v>1.541402013150962</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.50810540306326</v>
+        <v>-10.73345557041708</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.061689495120941</v>
+        <v>-1.15182956206247</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.549424176953093</v>
+        <v>-2.774774344306917</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.612254584246255</v>
+        <v>1.477044483833961</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.43463557139581</v>
+        <v>-10.65998573874963</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.01692986096054</v>
+        <v>-1.107069927902069</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.475954345285645</v>
+        <v>-2.701304512639468</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.671708184740145</v>
+        <v>1.536498084327852</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.60975998878235</v>
+        <v>-10.83511015613618</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.07242440716764</v>
+        <v>-1.162564474109169</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.651078762672189</v>
+        <v>-2.876428930026012</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.581188755055736</v>
+        <v>1.445978654643442</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.84421208279684</v>
+        <v>-11.06956225015067</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.173424409675032</v>
+        <v>-1.263564476616561</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.651078762672189</v>
+        <v>-2.876428930026012</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.57396959015414</v>
+        <v>1.438759489741846</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.13201592733408</v>
+        <v>-11.35736609468791</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.295218138263904</v>
+        <v>-1.385358205205434</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.938882607209427</v>
+        <v>-3.16423277456325</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.394615092657821</v>
+        <v>1.259404992245527</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.36184037449791</v>
+        <v>-11.58719054185173</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.386032127290878</v>
+        <v>-1.476172194232407</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.101530144279587</v>
+        <v>-3.326880311633411</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.298142360254281</v>
+        <v>1.162932259841987</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.59386929423417</v>
+        <v>-11.81921946158799</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.476149966556268</v>
+        <v>-1.566290033497797</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.16354284146801</v>
+        <v>-3.388893008821834</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.263628470570342</v>
+        <v>1.128418370158048</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.54185378026536</v>
+        <v>-11.76720394761918</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.451353425282341</v>
+        <v>-1.541493492223871</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.16354284146801</v>
+        <v>-3.388893008821834</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.267618806256742</v>
+        <v>1.132408705844449</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.68352562198948</v>
+        <v>-11.9088757893433</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.509497388870731</v>
+        <v>-1.59963745581226</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.16354284146801</v>
+        <v>-3.388893008821834</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.266143579358001</v>
+        <v>1.130933478945707</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.78243236244875</v>
+        <v>-12.00778252980258</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.534006674889569</v>
+        <v>-1.624146741831099</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.262449581927286</v>
+        <v>-3.487799749281109</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.221852945247308</v>
+        <v>1.086642844835014</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.58328025521165</v>
+        <v>-11.80863042256548</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.467396965641413</v>
+        <v>-1.557537032582942</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.097127055977472</v>
+        <v>-3.322477223331296</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.307995327170513</v>
+        <v>1.172785226758219</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.35743510249224</v>
+        <v>-11.58278526984607</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.36747983151744</v>
+        <v>-1.457619898458969</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.055200380390309</v>
+        <v>-3.280550547744133</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.34273040555902</v>
+        <v>1.207520305146725</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.07116029016955</v>
+        <v>-11.29651045752337</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.251830762032303</v>
+        <v>-1.341970828973832</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.055200380390309</v>
+        <v>-3.280550547744133</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.343869550115079</v>
+        <v>1.208659449702784</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.12405557821383</v>
+        <v>-11.34940574556766</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.27035510308791</v>
+        <v>-1.36049517002944</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.050245034301863</v>
+        <v>-3.275595201655686</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.349476531930254</v>
+        <v>1.21426643151796</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.84014684728509</v>
+        <v>-11.06549701463891</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.151057906477774</v>
+        <v>-1.241197973419303</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.050245034301863</v>
+        <v>-3.275595201655686</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.35521023616889</v>
+        <v>1.220000135756596</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.59315959709213</v>
+        <v>-10.81850976444596</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.062000268794458</v>
+        <v>-1.152140335735988</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.803257784108911</v>
+        <v>-3.028607951462734</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.493665323890796</v>
+        <v>1.358455223478502</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.32932272988806</v>
+        <v>-10.55467289724189</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9663490032257385</v>
+        <v>-1.056489070167268</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.803257784108911</v>
+        <v>-3.028607951462734</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.483781842577889</v>
+        <v>1.348571742165595</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.06208092901967</v>
+        <v>-10.28743109637349</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8612868433777527</v>
+        <v>-0.9514269103192823</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.803257784108911</v>
+        <v>-3.028607951462734</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.481947282078515</v>
+        <v>1.346737181666221</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.786271765619182</v>
+        <v>-10.01162193297301</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7512634929910198</v>
+        <v>-0.8414035599325493</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.714238475830177</v>
+        <v>-2.939588643184001</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.535058552072295</v>
+        <v>1.39984845166</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.762318224643224</v>
+        <v>-9.987668391997047</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7410135704551428</v>
+        <v>-0.8311536373966724</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.690284934854219</v>
+        <v>-2.915635102208043</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.550099182803363</v>
+        <v>1.414889082391068</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.498258286320427</v>
+        <v>-9.723608453674251</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6486499112877762</v>
+        <v>-0.7387899782293057</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.426224996531424</v>
+        <v>-2.651575163885247</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.695274829635288</v>
+        <v>1.560064729222994</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.791178662815589</v>
+        <v>-9.016528830169413</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3686050955461422</v>
+        <v>-0.4587451624876717</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.426224996531424</v>
+        <v>-2.651575163885247</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.692487795974987</v>
+        <v>1.557277695562693</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.750994364449399</v>
+        <v>-8.976344531803223</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3521877523118246</v>
+        <v>-0.4423278192533542</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.386040698165233</v>
+        <v>-2.611390865519057</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.716941998882543</v>
+        <v>1.581731898470249</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.670924568911595</v>
+        <v>-8.896274736265418</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3207930128759457</v>
+        <v>-0.4109330798174753</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.305970902627429</v>
+        <v>-2.531321069981253</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.764350697425982</v>
+        <v>1.629140597013688</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78732685376181</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.437443346681995</v>
+        <v>-8.837383986361466</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2194760951462538</v>
+        <v>-0.3794523510180423</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.07248968039783</v>
+        <v>-2.4724303200773</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.912363859601594</v>
+        <v>1.672399475793912</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.257734816538122</v>
+        <v>-8.657675456217593</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1504848934016634</v>
+        <v>-0.3104611492734519</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.015318176235134</v>
+        <v>-2.415258815914604</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.943774551786253</v>
+        <v>1.70381016797857</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860429</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.125459342907234</v>
+        <v>-8.525399982586706</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1022072172022814</v>
+        <v>-0.26218347307407</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.883042702604248</v>
+        <v>-2.282983342283718</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.018507322711812</v>
+        <v>1.778542938904129</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575955</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.934859668234082</v>
+        <v>-8.334800307913552</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.02315228664538393</v>
+        <v>-0.183128542517172</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.692443027931095</v>
+        <v>-2.092383667610565</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.13568218820334</v>
+        <v>1.895717804395657</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.75387899643099</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.685859869550501</v>
+        <v>-8.085800509229971</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.08935397405170731</v>
+        <v>-0.07062228182008079</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.692443027931095</v>
+        <v>-2.092383667610565</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.148588529426998</v>
+        <v>1.908624145619316</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077647</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.791449859323605</v>
+        <v>-8.191390499003075</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.08085795145675334</v>
+        <v>-0.2408342073285414</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.798033017704199</v>
+        <v>-2.19797365738367</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.957258605963917</v>
+        <v>1.717294222156235</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457905</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.810184761442202</v>
+        <v>-8.210125401121672</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.0398075704271057</v>
+        <v>-0.1997838262988938</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.798033017704199</v>
+        <v>-2.19797365738367</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.005802947841004</v>
+        <v>1.765838564033321</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180811</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.53344658677139</v>
+        <v>-7.93338722645086</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.07426671142721375</v>
+        <v>-0.0857095444445739</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.616216356594273</v>
+        <v>-2.016156996273744</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.118271956492954</v>
+        <v>1.878307572685271</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879204</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.40655418033632</v>
+        <v>-7.806494820015789</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.1163096877477638</v>
+        <v>-0.04366656812402381</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.489323950159203</v>
+        <v>-1.889264589838674</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.185693414100517</v>
+        <v>1.945729030292835</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568108</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.218966672426394</v>
+        <v>-7.618907312105863</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.1843840788166413</v>
+        <v>0.02440782294485322</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.489323950159203</v>
+        <v>-1.889264589838674</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.178732802005424</v>
+        <v>1.938768418197742</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78291895796342</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.976818278972535</v>
+        <v>-7.376758918652005</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.2957057905793277</v>
+        <v>0.1357295347075396</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.489323950159203</v>
+        <v>-1.889264589838674</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.193195156386567</v>
+        <v>1.953230772578885</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.913588907204187</v>
+        <v>-7.313529546883657</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3155296597458617</v>
+        <v>0.155553403874074</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.489323950159203</v>
+        <v>-1.889264589838674</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.187727276845762</v>
+        <v>1.94776289303808</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262049</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.727101214827181</v>
+        <v>-7.127041854506651</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.3876228307072411</v>
+        <v>0.2276465748354535</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.302836257782197</v>
+        <v>-1.702776897461668</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.297117986282543</v>
+        <v>2.057153602474861</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389911</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.705952015923738</v>
+        <v>-7.105892655603207</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4037834885059439</v>
+        <v>0.2438072326341563</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.281687058878754</v>
+        <v>-1.681627698558225</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.317508483861935</v>
+        <v>2.077544100054252</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788096</v>
+        <v>3.748324832788095</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.462186573940293</v>
+        <v>-6.862127213619763</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.4970703736463724</v>
+        <v>0.3370941177745848</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.281687058878754</v>
+        <v>-1.681627698558225</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.313289192208985</v>
+        <v>2.073324808401303</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527528</v>
+        <v>3.824307657527526</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.198158506747033</v>
+        <v>-6.598099146426502</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6048059144436926</v>
+        <v>0.4448296585719049</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.0798216600628</v>
+        <v>-1.479762299742271</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.436532745418573</v>
+        <v>2.196568361610891</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749186</v>
+        <v>3.826351398749185</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.948308112797958</v>
+        <v>-6.348248752477428</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6974881470070247</v>
+        <v>0.537511891135237</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.0798216600628</v>
+        <v>-1.479762299742271</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.429274820402275</v>
+        <v>2.189310436594593</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.8359544114815</v>
+        <v>3.835954411481498</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.64474062379398</v>
+        <v>-6.044681263473449</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8225142661292648</v>
+        <v>0.6625380102574772</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.0798216600628</v>
+        <v>-1.479762299742271</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.432873943922924</v>
+        <v>2.192909560115242</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862989</v>
+        <v>3.780930335862987</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.571260714941966</v>
+        <v>-5.971201354621435</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8652337357246243</v>
+        <v>0.7052574798528366</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.006341751210786</v>
+        <v>-1.406282390890257</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.490289395288686</v>
+        <v>2.250325011481004</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102784</v>
+        <v>3.773761647102782</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.346227715273143</v>
+        <v>-5.746168354952612</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9542674132084503</v>
+        <v>0.7942911573366627</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.7813087515419631</v>
+        <v>-1.181249391221434</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.624329672706277</v>
+        <v>2.384365288898595</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353079</v>
+        <v>3.764614304353077</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.131593337636736</v>
+        <v>-5.531533977316205</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.04481596531733</v>
+        <v>0.8848397094455427</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.5666743739055563</v>
+        <v>-0.9666150135850269</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.757805100342439</v>
+        <v>2.517840716534756</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544786</v>
+        <v>3.798811195544785</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.864992980662384</v>
+        <v>-5.264933620341854</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.132650366890867</v>
+        <v>0.9726741110190789</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.5666743739055563</v>
+        <v>-0.9666150135850269</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.738999359126234</v>
+        <v>2.499034975318552</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712298</v>
+        <v>3.797691308712296</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.624562483857524</v>
+        <v>-5.024503123536993</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.230565642237688</v>
+        <v>1.070589386365901</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.326243877100696</v>
+        <v>-0.7261845167801666</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.885000733834028</v>
+        <v>2.645036350026345</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837689</v>
+        <v>3.821589933837688</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.381771676208079</v>
+        <v>-4.781712315887548</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.331611279132287</v>
+        <v>1.171635023260499</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.326243877100696</v>
+        <v>-0.7261845167801666</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.888930047668848</v>
+        <v>2.648965663861166</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349971</v>
+        <v>3.822323422349969</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.142166584600989</v>
+        <v>-4.542107224280459</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.428131899692462</v>
+        <v>1.268155643820674</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.2591959294322015</v>
+        <v>-0.6591365691116721</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.929837400187285</v>
+        <v>2.689873016379603</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972345</v>
+        <v>3.848613050972343</v>
       </c>
       <c r="C1928" t="n">
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-3.899510996177826</v>
+        <v>-4.299451635857295</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.522192206281721</v>
+        <v>1.362215950409933</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.2591959294322015</v>
+        <v>-0.6591365691116721</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.926835471407278</v>
+        <v>2.686871087599596</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145945</v>
+        <v>3.818665376145943</v>
       </c>
       <c r="C1929" t="n">
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.679490198140815</v>
+        <v>-4.079430837820285</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.61177956250714</v>
+        <v>1.451803306635352</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.1179760843642212</v>
+        <v>-0.5179167240436918</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.013146415458681</v>
+        <v>2.773182031650998</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009957</v>
+        <v>3.843270952009955</v>
       </c>
       <c r="C1930" t="n">
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.480241568236006</v>
+        <v>-3.96771690076342</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.707373197270887</v>
+        <v>1.512383064259921</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.1179760843642212</v>
+        <v>-0.5179167240436918</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.029040598260504</v>
+        <v>2.789076214452821</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.874614466050418</v>
+        <v>3.578950257194901</v>
       </c>
       <c r="C1931" t="n">
-        <v>3.205223570616869</v>
+        <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.480241568236006</v>
+        <v>-3.802007428961446</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.707373197270887</v>
+        <v>1.579812697421012</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.1179760843642212</v>
+        <v>-0.352207252241718</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.198287367603237</v>
+        <v>2.889647741974307</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240411.xlsx
+++ b/tame_output/ON/bt/strategyON_20240411.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.3%</t>
+          <t>-77.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.5%</t>
+          <t>118.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.1%</t>
+          <t>137.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-708.1%</t>
+          <t>-716.7%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-56.1%</t>
+          <t>-56.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.2%</t>
+          <t>-73.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.4%</t>
+          <t>98.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>499.6%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-541.8%</t>
+          <t>-524.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-277.9%</t>
+          <t>-281.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-43.9%</t>
+          <t>-44.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-218.2%</t>
+          <t>-211.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.0%</t>
+          <t>-29.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-36.9%</t>
+          <t>-37.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.9%</t>
+          <t>-22.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-152.7%</t>
+          <t>-152.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-259.2%</t>
+          <t>-250.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>97.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-31.9%</t>
+          <t>-32.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-157.1%</t>
+          <t>-151.7%</t>
         </is>
       </c>
     </row>
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.153375272995</v>
+        <v>-10.23917305058595</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.9328349453184841</v>
+        <v>-0.9671540563548651</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.313527906130268</v>
+        <v>-2.39932568372122</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.740754844515103</v>
+        <v>1.689276177960532</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.37224929355527</v>
+        <v>-10.45832201866015</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.017342802920821</v>
+        <v>-1.051771892962775</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.532401926690532</v>
+        <v>-2.618474651795417</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.612472182800714</v>
+        <v>1.560828547737782</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.36855836859885</v>
+        <v>-10.45463109370374</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.015866432938257</v>
+        <v>-1.050295522980211</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.532401926690532</v>
+        <v>-2.618474651795417</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.612472182800714</v>
+        <v>1.560828547737782</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.57281654392872</v>
+        <v>-10.6588892690336</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.09205650595156</v>
+        <v>-1.126485595993514</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.660040871304521</v>
+        <v>-2.746113596409406</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.541402013150962</v>
+        <v>1.489758378088031</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.73345557041708</v>
+        <v>-10.81952829552197</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.15182956206247</v>
+        <v>-1.186258652104424</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.774774344306917</v>
+        <v>-2.860847069411802</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.477044483833961</v>
+        <v>1.42540084877103</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.65998573874963</v>
+        <v>-10.74605846385452</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.107069927902069</v>
+        <v>-1.141499017944023</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.701304512639468</v>
+        <v>-2.787377237744353</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.536498084327852</v>
+        <v>1.48485444926492</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.83511015613618</v>
+        <v>-10.92118288124106</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.162564474109169</v>
+        <v>-1.196993564151123</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.876428930026012</v>
+        <v>-2.962501655130897</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.445978654643442</v>
+        <v>1.394335019580511</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.06956225015067</v>
+        <v>-11.15563497525555</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.263564476616561</v>
+        <v>-1.297993566658515</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.876428930026012</v>
+        <v>-2.962501655130897</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.438759489741846</v>
+        <v>1.387115854678915</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.35736609468791</v>
+        <v>-11.44343881979279</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.385358205205434</v>
+        <v>-1.419787295247387</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.16423277456325</v>
+        <v>-3.250305499668135</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.259404992245527</v>
+        <v>1.207761357182596</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.58719054185173</v>
+        <v>-11.67326326695662</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.476172194232407</v>
+        <v>-1.510601284274361</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.326880311633411</v>
+        <v>-3.412953036738296</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.162932259841987</v>
+        <v>1.111288624779056</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.81921946158799</v>
+        <v>-11.90529218669288</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.566290033497797</v>
+        <v>-1.600719123539751</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.388893008821834</v>
+        <v>-3.474965733926719</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.128418370158048</v>
+        <v>1.076774735095117</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.76720394761918</v>
+        <v>-11.85327667272406</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.541493492223871</v>
+        <v>-1.575922582265824</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.388893008821834</v>
+        <v>-3.474965733926719</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.132408705844449</v>
+        <v>1.080765070781518</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.9088757893433</v>
+        <v>-11.99494851444818</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.59963745581226</v>
+        <v>-1.634066545854214</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.388893008821834</v>
+        <v>-3.474965733926719</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.130933478945707</v>
+        <v>1.079289843882776</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.00778252980258</v>
+        <v>-12.09385525490746</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.624146741831099</v>
+        <v>-1.658575831873053</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.487799749281109</v>
+        <v>-3.573872474385995</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.086642844835014</v>
+        <v>1.034999209772082</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.80863042256548</v>
+        <v>-11.89470314767036</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.557537032582942</v>
+        <v>-1.591966122624896</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.322477223331296</v>
+        <v>-3.408549948436181</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.172785226758219</v>
+        <v>1.121141591695288</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.58278526984607</v>
+        <v>-11.66885799495095</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.457619898458969</v>
+        <v>-1.492048988500923</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.280550547744133</v>
+        <v>-3.366623272849018</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.207520305146725</v>
+        <v>1.155876670083794</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.29651045752337</v>
+        <v>-11.38258318262826</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.341970828973832</v>
+        <v>-1.376399919015786</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.280550547744133</v>
+        <v>-3.366623272849018</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.208659449702784</v>
+        <v>1.157015814639853</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.34940574556766</v>
+        <v>-11.43547847067254</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.36049517002944</v>
+        <v>-1.394924260071393</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.275595201655686</v>
+        <v>-3.361667926760572</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.21426643151796</v>
+        <v>1.162622796455028</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.06549701463891</v>
+        <v>-11.15156973974379</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.241197973419303</v>
+        <v>-1.275627063461257</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.275595201655686</v>
+        <v>-3.361667926760572</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.220000135756596</v>
+        <v>1.168356500693665</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.81850976444596</v>
+        <v>-10.90458248955084</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.152140335735988</v>
+        <v>-1.186569425777941</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.028607951462734</v>
+        <v>-3.11468067656762</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.358455223478502</v>
+        <v>1.306811588415571</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.55467289724189</v>
+        <v>-10.64074562234677</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.056489070167268</v>
+        <v>-1.090918160209222</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.028607951462734</v>
+        <v>-3.11468067656762</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.348571742165595</v>
+        <v>1.296928107102663</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.28743109637349</v>
+        <v>-10.37350382147837</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9514269103192823</v>
+        <v>-0.985856000361236</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.028607951462734</v>
+        <v>-3.11468067656762</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.346737181666221</v>
+        <v>1.29509354660329</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.01162193297301</v>
+        <v>-10.09769465807789</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8414035599325493</v>
+        <v>-0.8758326499745031</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.939588643184001</v>
+        <v>-3.025661368288886</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.39984845166</v>
+        <v>1.348204816597069</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.987668391997047</v>
+        <v>-10.07374111710193</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8311536373966724</v>
+        <v>-0.8655827274386261</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.915635102208043</v>
+        <v>-3.001707827312929</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.414889082391068</v>
+        <v>1.363245447328137</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.723608453674251</v>
+        <v>-9.809681178779135</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7387899782293057</v>
+        <v>-0.7732190682712594</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.651575163885247</v>
+        <v>-2.737647888990133</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.560064729222994</v>
+        <v>1.508421094160063</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.016528830169413</v>
+        <v>-9.102601555274298</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4587451624876717</v>
+        <v>-0.4931742525296254</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.651575163885247</v>
+        <v>-2.737647888990133</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.557277695562693</v>
+        <v>1.505634060499762</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.976344531803223</v>
+        <v>-9.062417256908107</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4423278192533542</v>
+        <v>-0.4767569092953079</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.611390865519057</v>
+        <v>-2.697463590623942</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.581731898470249</v>
+        <v>1.530088263407318</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.896274736265418</v>
+        <v>-8.982347461370303</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4109330798174753</v>
+        <v>-0.445362169859429</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.531321069981253</v>
+        <v>-2.617393795086138</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.629140597013688</v>
+        <v>1.577496961950757</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.837383986361466</v>
+        <v>-8.748866239140703</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3794523510180423</v>
+        <v>-0.344045252129737</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.4724303200773</v>
+        <v>-2.383912572856539</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.672399475793912</v>
+        <v>1.725510124126368</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.657675456217593</v>
+        <v>-8.56915770899683</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3104611492734519</v>
+        <v>-0.2750540503851466</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.415258815914604</v>
+        <v>-2.326741068693843</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.70381016797857</v>
+        <v>1.756920816311027</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.525399982586706</v>
+        <v>-8.436882235365943</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.26218347307407</v>
+        <v>-0.2267763741857647</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.282983342283718</v>
+        <v>-2.194465595062957</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.778542938904129</v>
+        <v>1.831653587236586</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.334800307913552</v>
+        <v>-8.246282560692789</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.183128542517172</v>
+        <v>-0.1477214436288667</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.092383667610565</v>
+        <v>-2.003865920389804</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.895717804395657</v>
+        <v>1.948828452728114</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.085800509229971</v>
+        <v>-7.997282762009208</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.07062228182008079</v>
+        <v>-0.0352151829317755</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.092383667610565</v>
+        <v>-2.003865920389804</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.908624145619316</v>
+        <v>1.961734793951773</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.191390499003075</v>
+        <v>-8.102872751782312</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2408342073285414</v>
+        <v>-0.2054271084402362</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.19797365738367</v>
+        <v>-2.109455910162908</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.717294222156235</v>
+        <v>1.770404870488692</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.210125401121672</v>
+        <v>-8.121607653900909</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1997838262988938</v>
+        <v>-0.1643767274105885</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.19797365738367</v>
+        <v>-2.109455910162908</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.765838564033321</v>
+        <v>1.818949212365778</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.93338722645086</v>
+        <v>-7.844869479230097</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.0857095444445739</v>
+        <v>-0.05030244555626862</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.016156996273744</v>
+        <v>-1.927639249052982</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.878307572685271</v>
+        <v>1.931418221017728</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.806494820015789</v>
+        <v>-7.717977072795026</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.04366656812402381</v>
+        <v>-0.008259469235718964</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.889264589838674</v>
+        <v>-1.800746842617913</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.945729030292835</v>
+        <v>1.998839678625292</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.618907312105863</v>
+        <v>-7.5303895648851</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.02440782294485322</v>
+        <v>0.05981492183315851</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.889264589838674</v>
+        <v>-1.800746842617913</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.938768418197742</v>
+        <v>1.991879066530199</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.376758918652005</v>
+        <v>-7.288241171431242</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1357295347075396</v>
+        <v>0.1711366335958449</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.889264589838674</v>
+        <v>-1.800746842617913</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.953230772578885</v>
+        <v>2.006341420911342</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.313529546883657</v>
+        <v>-7.225011799662894</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.155553403874074</v>
+        <v>0.1909605027623793</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.889264589838674</v>
+        <v>-1.800746842617913</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.94776289303808</v>
+        <v>2.000873541370537</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.127041854506651</v>
+        <v>-7.038524107285888</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2276465748354535</v>
+        <v>0.2630536737237588</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.702776897461668</v>
+        <v>-1.614259150240906</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.057153602474861</v>
+        <v>2.110264250807317</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.105892655603207</v>
+        <v>-7.017374908382444</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2438072326341563</v>
+        <v>0.2792143315224616</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.681627698558225</v>
+        <v>-1.593109951337463</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.077544100054252</v>
+        <v>2.130654748386709</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.862127213619763</v>
+        <v>-6.773609466399</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3370941177745848</v>
+        <v>0.37250121666289</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.681627698558225</v>
+        <v>-1.593109951337463</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.073324808401303</v>
+        <v>2.12643545673376</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.598099146426502</v>
+        <v>-6.509581399205739</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4448296585719049</v>
+        <v>0.4802367574602102</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.479762299742271</v>
+        <v>-1.391244552521509</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.196568361610891</v>
+        <v>2.249679009943348</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.348248752477428</v>
+        <v>-6.259731005256665</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.537511891135237</v>
+        <v>0.5729189900235423</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.479762299742271</v>
+        <v>-1.391244552521509</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.189310436594593</v>
+        <v>2.24242108492705</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.044681263473449</v>
+        <v>-5.956163516252686</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.6625380102574772</v>
+        <v>0.6979451091457824</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.479762299742271</v>
+        <v>-1.391244552521509</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.192909560115242</v>
+        <v>2.246020208447699</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.971201354621435</v>
+        <v>-5.882683607400672</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.7052574798528366</v>
+        <v>0.7406645787411419</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.406282390890257</v>
+        <v>-1.317764643669495</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.250325011481004</v>
+        <v>2.303435659813461</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.746168354952612</v>
+        <v>-5.657650607731849</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7942911573366627</v>
+        <v>0.829698256224968</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.181249391221434</v>
+        <v>-1.092731644000672</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.384365288898595</v>
+        <v>2.437475937231052</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.531533977316205</v>
+        <v>-5.443016230095442</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8848397094455427</v>
+        <v>0.920246808333848</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9666150135850269</v>
+        <v>-0.8780972663642652</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.517840716534756</v>
+        <v>2.570951364867213</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.264933620341854</v>
+        <v>-5.176415873121091</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9726741110190789</v>
+        <v>1.008081209907384</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9666150135850269</v>
+        <v>-0.8780972663642652</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.499034975318552</v>
+        <v>2.552145623651009</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.024503123536993</v>
+        <v>-4.93598537631623</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.070589386365901</v>
+        <v>1.105996485254206</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7261845167801666</v>
+        <v>-0.6376667695594049</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.645036350026345</v>
+        <v>2.698146998358802</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.781712315887548</v>
+        <v>-4.693194568666785</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.171635023260499</v>
+        <v>1.207042122148804</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7261845167801666</v>
+        <v>-0.6376667695594049</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.648965663861166</v>
+        <v>2.702076312193622</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.542107224280459</v>
+        <v>-4.453589477059696</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.268155643820674</v>
+        <v>1.30356274270898</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6591365691116721</v>
+        <v>-0.5706188218909104</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.689873016379603</v>
+        <v>2.742983664712059</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.299451635857295</v>
+        <v>-4.210933888636532</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.362215950409933</v>
+        <v>1.397623049298239</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6591365691116721</v>
+        <v>-0.5706188218909104</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.686871087599596</v>
+        <v>2.739981735932053</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.079430837820285</v>
+        <v>-3.990913090599521</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.451803306635352</v>
+        <v>1.487210405523657</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5179167240436918</v>
+        <v>-0.4293989768229302</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.773182031650998</v>
+        <v>2.826292679983455</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.96771690076342</v>
+        <v>-3.791664460694712</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.512383064259921</v>
+        <v>1.582804040287404</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5179167240436918</v>
+        <v>-0.4293989768229302</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.789076214452821</v>
+        <v>2.842186862785279</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.802007428961446</v>
+        <v>-3.624739748478794</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.579812697421012</v>
+        <v>1.650719769614073</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.352207252241718</v>
+        <v>-0.2624742646070115</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.889647741974307</v>
+        <v>2.943487534555131</v>
       </c>
     </row>
   </sheetData>
